--- a/public/sap-reporting/expansion-150-downloads/EXT-QM06-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM06-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rb30171ed23c34cf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R4ca3a636051049d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Re3ff500b47944198"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R9c893b03ad4143b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Re4f0ead8a9104c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rba0183010be54a0e"/>
   </x:sheets>
 </x:workbook>
 </file>
